--- a/data/administracion_de_tribunales/OP_LEY148Denegadas.xlsx
+++ b/data/administracion_de_tribunales/OP_LEY148Denegadas.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82440BA3-EFD3-480F-934C-3026B8EFE026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEA07A3-78D8-45EF-B9A1-04B175E39E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="9420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="4" r:id="rId1"/>
     <sheet name="2021-2022" sheetId="1" r:id="rId2"/>
     <sheet name="2022-2023" sheetId="2" r:id="rId3"/>
     <sheet name="2023-2024" sheetId="3" r:id="rId4"/>
+    <sheet name="2024-2025" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="21">
   <si>
     <t>Región</t>
   </si>
@@ -138,9 +139,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,64 +449,54 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1"/>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
     </row>
@@ -514,14 +504,13 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -529,48 +518,30 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
     </row>
@@ -578,21 +549,15 @@
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>1</v>
       </c>
     </row>
@@ -600,19 +565,19 @@
       <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <f>SUM(B3:B14)</f>
         <v>13</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <f>SUM(C3:C14)</f>
         <v>4</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <f>SUM(D3:D14)</f>
         <v>4</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <f>SUM(E3:E14)</f>
         <v>5</v>
       </c>
@@ -652,69 +617,53 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
-      <c r="E3" s="1"/>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1">
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -722,63 +671,44 @@
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1"/>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>2</v>
       </c>
     </row>
@@ -786,32 +716,30 @@
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1"/>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <f>SUM(B3:B14)</f>
         <v>11</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <f>SUM(C3:C14)</f>
         <v>4</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <f>SUM(D3:D14)</f>
         <v>4</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <f>SUM(E3:E14)</f>
         <v>3</v>
       </c>
@@ -852,52 +780,36 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
@@ -905,34 +817,26 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
     </row>
@@ -940,34 +844,26 @@
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1"/>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
     </row>
@@ -975,14 +871,13 @@
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
     </row>
@@ -990,12 +885,10 @@
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="E14">
         <v>2</v>
       </c>
     </row>
@@ -1003,19 +896,19 @@
       <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <f>SUM(B3:B14)</f>
         <v>10</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15">
         <f>SUM(C3:C14)</f>
         <v>2</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15">
         <f>SUM(D3:D14)</f>
         <v>2</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <f>SUM(E3:E14)</f>
         <v>6</v>
       </c>
@@ -1055,70 +948,42 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1">
-        <v>2</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2</v>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
@@ -1126,109 +991,256 @@
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="1">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="1">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <f>SUM(B3:B14)</f>
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <f>SUM(C3:C14)</f>
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <f>SUM(D3:D14)</f>
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <f>SUM(E3:E14)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2A9B8A-292C-45E7-8351-57F72AFCC6AF}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="4" max="4" width="35.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="1">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <f>SUM(B3:B14)</f>
+        <v>20</v>
+      </c>
+      <c r="C15">
         <f>SUM(C3:C14)</f>
-        <v>3</v>
-      </c>
-      <c r="D15" s="1">
+        <v>6</v>
+      </c>
+      <c r="D15">
         <f>SUM(D3:D14)</f>
+        <v>8</v>
+      </c>
+      <c r="E15">
+        <f>SUM(E3:E14)</f>
         <v>6</v>
-      </c>
-      <c r="E15" s="1">
-        <f>SUM(E3:E14)</f>
-        <v>7</v>
       </c>
     </row>
   </sheetData>
